--- a/stations/output/MAF_Interlocking_Program.xlsx
+++ b/stations/output/MAF_Interlocking_Program.xlsx
@@ -1206,7 +1206,7 @@
       <c r="E3" s="49" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v0.24.1</t>
+          <t>v1.0.0</t>
         </is>
       </c>
     </row>

--- a/stations/output/MAF_Interlocking_Program.xlsx
+++ b/stations/output/MAF_Interlocking_Program.xlsx
@@ -1206,7 +1206,7 @@
       <c r="E3" s="49" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v1.0.0</t>
+          <t>v1.0.1</t>
         </is>
       </c>
     </row>

--- a/stations/output/MAF_Interlocking_Program.xlsx
+++ b/stations/output/MAF_Interlocking_Program.xlsx
@@ -22008,7 +22008,7 @@
       </c>
       <c r="C1" s="36" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Operational Parameters</t>
         </is>
       </c>
       <c r="D1" s="37" t="inlineStr">

--- a/stations/output/MAF_Interlocking_Program.xlsx
+++ b/stations/output/MAF_Interlocking_Program.xlsx
@@ -462,15 +462,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color theme="1"/>
@@ -479,37 +470,6 @@
         <color theme="1"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -531,30 +491,6 @@
       <top style="thin">
         <color theme="1"/>
       </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color theme="1"/>
       </bottom>
@@ -585,6 +521,39 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color theme="1"/>
@@ -592,6 +561,15 @@
       <top style="medium">
         <color theme="1"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -609,6 +587,17 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color theme="1"/>
@@ -639,12 +628,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -788,9 +788,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -818,29 +815,42 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1183,49 +1193,49 @@
       <c r="B1" s="21" t="n"/>
       <c r="C1" s="21" t="n"/>
       <c r="D1" s="21" t="n"/>
-      <c r="E1" s="59" t="inlineStr">
+      <c r="E1" s="61" t="inlineStr">
         <is>
           <t>ZIRCON</t>
         </is>
       </c>
-      <c r="F1" s="60" t="n"/>
+      <c r="F1" s="62" t="n"/>
     </row>
     <row r="2" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A2" s="22" t="n"/>
-      <c r="B2" s="49" t="n"/>
-      <c r="C2" s="49" t="n"/>
-      <c r="D2" s="49" t="n"/>
-      <c r="E2" s="61" t="n"/>
-      <c r="F2" s="62" t="n"/>
+      <c r="A2" s="58" t="n"/>
+      <c r="B2" s="59" t="n"/>
+      <c r="C2" s="59" t="n"/>
+      <c r="D2" s="59" t="n"/>
+      <c r="E2" s="63" t="n"/>
+      <c r="F2" s="64" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="n"/>
-      <c r="B3" s="49" t="n"/>
-      <c r="C3" s="49" t="n"/>
-      <c r="D3" s="49" t="n"/>
-      <c r="E3" s="49" t="n"/>
+      <c r="A3" s="58" t="n"/>
+      <c r="B3" s="59" t="n"/>
+      <c r="C3" s="59" t="n"/>
+      <c r="D3" s="59" t="n"/>
+      <c r="E3" s="59" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v1.0.1</t>
+          <t>v1.0.2</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="n"/>
-      <c r="B4" s="49" t="n"/>
-      <c r="C4" s="49" t="n"/>
-      <c r="D4" s="49" t="n"/>
-      <c r="E4" s="49" t="n"/>
-      <c r="F4" s="23" t="n"/>
+      <c r="A4" s="58" t="n"/>
+      <c r="B4" s="59" t="n"/>
+      <c r="C4" s="59" t="n"/>
+      <c r="D4" s="59" t="n"/>
+      <c r="E4" s="59" t="n"/>
+      <c r="F4" s="60" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="n"/>
+      <c r="A5" s="58" t="n"/>
       <c r="B5" s="48" t="inlineStr">
         <is>
           <t>Interlocking Program</t>
         </is>
       </c>
-      <c r="F5" s="23" t="n"/>
+      <c r="F5" s="60" t="n"/>
     </row>
     <row r="6" ht="14.4" customHeight="1">
       <c r="A6" s="24" t="n"/>
@@ -1240,94 +1250,92 @@
       <c r="F7" s="25" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="n"/>
-      <c r="B8" s="49" t="inlineStr">
-        <is>
-          <t>Mafra (MAF)</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="n"/>
+      <c r="A8" s="65" t="inlineStr">
+        <is>
+          <t>Mafra (NOT REAL DATA - FOR TESTING ONLY) (MAF)</t>
+        </is>
+      </c>
+      <c r="F8" s="66" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="n"/>
-      <c r="B9" s="49" t="inlineStr">
+      <c r="A9" s="65" t="inlineStr">
         <is>
           <t>Linha do Oeste</t>
         </is>
       </c>
-      <c r="F9" s="23" t="n"/>
+      <c r="F9" s="66" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="n"/>
-      <c r="B10" s="49" t="n"/>
-      <c r="C10" s="49" t="n"/>
-      <c r="D10" s="49" t="n"/>
-      <c r="E10" s="49" t="n"/>
-      <c r="F10" s="23" t="n"/>
+      <c r="A10" s="58" t="n"/>
+      <c r="B10" s="59" t="n"/>
+      <c r="C10" s="59" t="n"/>
+      <c r="D10" s="59" t="n"/>
+      <c r="E10" s="59" t="n"/>
+      <c r="F10" s="60" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="n"/>
-      <c r="B11" s="49" t="n"/>
-      <c r="C11" s="49" t="n"/>
-      <c r="D11" s="49" t="n"/>
-      <c r="E11" s="49" t="n"/>
-      <c r="F11" s="23" t="n"/>
+      <c r="A11" s="58" t="n"/>
+      <c r="B11" s="59" t="n"/>
+      <c r="C11" s="59" t="n"/>
+      <c r="D11" s="59" t="n"/>
+      <c r="E11" s="59" t="n"/>
+      <c r="F11" s="60" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="n"/>
-      <c r="B12" s="49" t="n"/>
-      <c r="C12" s="49" t="n"/>
-      <c r="D12" s="49" t="n"/>
-      <c r="E12" s="49" t="n"/>
-      <c r="F12" s="23" t="n"/>
+      <c r="A12" s="58" t="n"/>
+      <c r="B12" s="59" t="n"/>
+      <c r="C12" s="59" t="n"/>
+      <c r="D12" s="59" t="n"/>
+      <c r="E12" s="59" t="n"/>
+      <c r="F12" s="60" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="n"/>
-      <c r="B13" s="49" t="n"/>
-      <c r="C13" s="49" t="n"/>
-      <c r="D13" s="49" t="n"/>
-      <c r="E13" s="49" t="n"/>
-      <c r="F13" s="23" t="n"/>
+      <c r="A13" s="58" t="n"/>
+      <c r="B13" s="59" t="n"/>
+      <c r="C13" s="59" t="n"/>
+      <c r="D13" s="59" t="n"/>
+      <c r="E13" s="59" t="n"/>
+      <c r="F13" s="60" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="n"/>
-      <c r="B14" s="49" t="n"/>
-      <c r="C14" s="49" t="n"/>
-      <c r="D14" s="49" t="n"/>
-      <c r="E14" s="49" t="n"/>
-      <c r="F14" s="23" t="n"/>
+      <c r="A14" s="58" t="n"/>
+      <c r="B14" s="59" t="n"/>
+      <c r="C14" s="59" t="n"/>
+      <c r="D14" s="59" t="n"/>
+      <c r="E14" s="59" t="n"/>
+      <c r="F14" s="60" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="n"/>
-      <c r="B15" s="49" t="n"/>
-      <c r="C15" s="49" t="n"/>
-      <c r="D15" s="49" t="n"/>
-      <c r="E15" s="49" t="n"/>
-      <c r="F15" s="23" t="n"/>
+      <c r="A15" s="58" t="n"/>
+      <c r="B15" s="59" t="n"/>
+      <c r="C15" s="59" t="n"/>
+      <c r="D15" s="59" t="n"/>
+      <c r="E15" s="59" t="n"/>
+      <c r="F15" s="60" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="n"/>
-      <c r="B16" s="49" t="n"/>
-      <c r="C16" s="49" t="n"/>
-      <c r="D16" s="49" t="n"/>
-      <c r="E16" s="49" t="n"/>
-      <c r="F16" s="23" t="n"/>
+      <c r="A16" s="58" t="n"/>
+      <c r="B16" s="59" t="n"/>
+      <c r="C16" s="59" t="n"/>
+      <c r="D16" s="59" t="n"/>
+      <c r="E16" s="59" t="n"/>
+      <c r="F16" s="60" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="n"/>
-      <c r="B17" s="49" t="n"/>
-      <c r="C17" s="49" t="n"/>
-      <c r="D17" s="49" t="n"/>
-      <c r="E17" s="49" t="n"/>
-      <c r="F17" s="23" t="n"/>
+      <c r="A17" s="58" t="n"/>
+      <c r="B17" s="59" t="n"/>
+      <c r="C17" s="59" t="n"/>
+      <c r="D17" s="59" t="n"/>
+      <c r="E17" s="59" t="n"/>
+      <c r="F17" s="60" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="n"/>
-      <c r="B18" s="49" t="n"/>
-      <c r="C18" s="49" t="n"/>
-      <c r="D18" s="49" t="n"/>
-      <c r="E18" s="49" t="n"/>
-      <c r="F18" s="23" t="n"/>
+      <c r="A18" s="58" t="n"/>
+      <c r="B18" s="59" t="n"/>
+      <c r="C18" s="59" t="n"/>
+      <c r="D18" s="59" t="n"/>
+      <c r="E18" s="59" t="n"/>
+      <c r="F18" s="60" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="30" t="inlineStr">
@@ -1335,11 +1343,11 @@
           <t>Diogo Luís</t>
         </is>
       </c>
-      <c r="B19" s="49" t="n"/>
-      <c r="C19" s="49" t="n"/>
-      <c r="D19" s="49" t="n"/>
-      <c r="E19" s="49" t="n"/>
-      <c r="F19" s="23" t="n"/>
+      <c r="B19" s="59" t="n"/>
+      <c r="C19" s="59" t="n"/>
+      <c r="D19" s="59" t="n"/>
+      <c r="E19" s="59" t="n"/>
+      <c r="F19" s="60" t="n"/>
     </row>
     <row r="20" ht="16.2" customHeight="1" thickBot="1">
       <c r="A20" s="31" t="inlineStr">
@@ -1355,9 +1363,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A8:F8"/>
     <mergeCell ref="B5:E6"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A9:F9"/>
     <mergeCell ref="E1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1385,310 +1393,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -1715,7 +1723,7 @@
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -1744,7 +1752,7 @@
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr">
         <is>
-          <t>1, II</t>
+          <t>1, LII</t>
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr">
@@ -1782,7 +1790,7 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
@@ -1837,7 +1845,7 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -1866,7 +1874,7 @@
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr">
         <is>
-          <t>1, I</t>
+          <t>1, LI</t>
         </is>
       </c>
       <c r="S8" s="12" t="inlineStr">
@@ -1904,7 +1912,7 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -1959,7 +1967,7 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -1988,7 +1996,7 @@
       <c r="Q10" s="12" t="inlineStr"/>
       <c r="R10" s="11" t="inlineStr">
         <is>
-          <t>2, II</t>
+          <t>2, LII</t>
         </is>
       </c>
       <c r="S10" s="12" t="inlineStr">
@@ -2026,7 +2034,7 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
@@ -2081,7 +2089,7 @@
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
@@ -2110,7 +2118,7 @@
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr">
         <is>
-          <t>2, I</t>
+          <t>2, LI</t>
         </is>
       </c>
       <c r="S12" s="12" t="inlineStr">
@@ -2148,7 +2156,7 @@
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
@@ -4899,310 +4907,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -5219,7 +5227,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -5282,7 +5290,7 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -5341,7 +5349,7 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -5404,7 +5412,7 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -5463,7 +5471,7 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -5526,7 +5534,7 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -5585,7 +5593,7 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -5648,7 +5656,7 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -8413,310 +8421,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -11671,310 +11679,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -14929,310 +14937,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -18187,310 +18195,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -21438,24 +21446,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="B1" s="66" t="n"/>
-      <c r="C1" s="55" t="inlineStr">
+      <c r="B1" s="70" t="n"/>
+      <c r="C1" s="54" t="inlineStr">
         <is>
           <t>Approach Route Cancel</t>
         </is>
       </c>
-      <c r="D1" s="66" t="n"/>
-      <c r="E1" s="55" t="inlineStr">
+      <c r="D1" s="70" t="n"/>
+      <c r="E1" s="54" t="inlineStr">
         <is>
           <t>Emergency Route Cancel</t>
         </is>
       </c>
-      <c r="F1" s="66" t="n"/>
+      <c r="F1" s="70" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -21463,27 +21471,27 @@
           <t>Track</t>
         </is>
       </c>
-      <c r="B2" s="50" t="inlineStr">
+      <c r="B2" s="49" t="inlineStr">
         <is>
           <t>Delay [s]</t>
         </is>
       </c>
-      <c r="C2" s="50" t="inlineStr">
+      <c r="C2" s="49" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="D2" s="50" t="inlineStr">
+      <c r="D2" s="49" t="inlineStr">
         <is>
           <t>Delay [s]</t>
         </is>
       </c>
-      <c r="E2" s="50" t="inlineStr">
+      <c r="E2" s="49" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="F2" s="57" t="inlineStr">
+      <c r="F2" s="56" t="inlineStr">
         <is>
           <t>Delay [s]</t>
         </is>
@@ -21492,7 +21500,7 @@
     <row r="3">
       <c r="A3" s="32" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="B3" s="12" t="n">
@@ -21518,7 +21526,7 @@
     <row r="4">
       <c r="A4" s="32" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="B4" s="12" t="n">
@@ -22038,7 +22046,7 @@
       </c>
       <c r="D2" s="40" t="inlineStr">
         <is>
-          <t xml:space="preserve">station_name Mafra
+          <t xml:space="preserve">station_name Mafra (NOT REAL DATA - FOR TESTING ONLY)
 </t>
         </is>
       </c>
@@ -22052,7 +22060,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1 33043 33043 32747
+          <t xml:space="preserve">    1 3043 3043 2747
 </t>
         </is>
       </c>
@@ -22072,13 +22080,13 @@
     <row r="4">
       <c r="A4" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NDE A I
+          <t xml:space="preserve">    NDE A LI
 </t>
         </is>
       </c>
       <c r="B4" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    I 33272 33043
+          <t xml:space="preserve">    LI 3272 3043
 </t>
         </is>
       </c>
@@ -22104,7 +22112,7 @@
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    II 33272 33043
+          <t xml:space="preserve">    LII 3272 3043
 </t>
         </is>
       </c>
@@ -22130,7 +22138,7 @@
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2 33573 33272 33272
+          <t xml:space="preserve">    2 3573 3272 3272
 </t>
         </is>
       </c>
@@ -22150,7 +22158,7 @@
     <row r="7">
       <c r="A7" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NDE B II
+          <t xml:space="preserve">    NDE B LII
 </t>
         </is>
       </c>
@@ -22177,7 +22185,7 @@
       </c>
       <c r="B8" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1 32958 33028
+          <t xml:space="preserve">    1 2958 3028
 </t>
         </is>
       </c>
@@ -22198,7 +22206,7 @@
       </c>
       <c r="B9" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2 33370 33315
+          <t xml:space="preserve">    2 3370 3315
 </t>
         </is>
       </c>
@@ -22234,13 +22242,13 @@
     <row r="11">
       <c r="A11" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEC I
+          <t xml:space="preserve">SEC LI
 </t>
         </is>
       </c>
       <c r="B11" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S1 32739 31175 350
+          <t xml:space="preserve">    S1 2739 1175 350
 </t>
         </is>
       </c>
@@ -22261,7 +22269,7 @@
       </c>
       <c r="B12" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S6 33048 35250 350
+          <t xml:space="preserve">    S6 3048 5250 350
 </t>
         </is>
       </c>
@@ -22282,7 +22290,7 @@
       </c>
       <c r="B13" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S4 33048 35250 350
+          <t xml:space="preserve">    S4 3048 5250 350
 </t>
         </is>
       </c>
@@ -22297,13 +22305,13 @@
     <row r="14">
       <c r="A14" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEC II
+          <t xml:space="preserve">SEC LII
 </t>
         </is>
       </c>
       <c r="B14" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S5 33267 31175 350
+          <t xml:space="preserve">    S5 3267 1175 350
 </t>
         </is>
       </c>
@@ -22324,7 +22332,7 @@
       </c>
       <c r="B15" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S3 33267 31175 350
+          <t xml:space="preserve">    S3 3267 1175 350
 </t>
         </is>
       </c>
@@ -22345,7 +22353,7 @@
       </c>
       <c r="B16" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S2 33581 35250 350
+          <t xml:space="preserve">    S2 3581 5250 350
 </t>
         </is>
       </c>
@@ -22405,7 +22413,7 @@
     <row r="20">
       <c r="A20" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NDE B II
+          <t xml:space="preserve">    NDE B LII
 </t>
         </is>
       </c>
@@ -22435,7 +22443,7 @@
     <row r="22">
       <c r="A22" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NDE C I
+          <t xml:space="preserve">    NDE C LI
 </t>
         </is>
       </c>
